--- a/3. G_Documents/4. Tài liệu/TrackerDocs.xlsx
+++ b/3. G_Documents/4. Tài liệu/TrackerDocs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3.G_Documents\4.Tài liệu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5245F0E-7480-4C64-998A-7FF8038F4417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1DAE6F-0768-4F98-ABED-96B135919FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{B1651102-A924-47AC-8049-DF1B6F725B88}"/>
   </bookViews>

--- a/3. G_Documents/4. Tài liệu/TrackerDocs.xlsx
+++ b/3. G_Documents/4. Tài liệu/TrackerDocs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1DAE6F-0768-4F98-ABED-96B135919FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A118F0C-8A41-49F5-B59E-C0925AFFD1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{B1651102-A924-47AC-8049-DF1B6F725B88}"/>
   </bookViews>
